--- a/output/pdf_financials_xlsx/RAIL.xlsx
+++ b/output/pdf_financials_xlsx/RAIL.xlsx
@@ -982,13 +982,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.67294</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>1.668521</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.752474</v>
       </c>
     </row>
     <row r="35">
@@ -1014,13 +1014,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.67294</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>1.668521</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.752474</v>
       </c>
     </row>
     <row r="37">
@@ -1206,13 +1206,13 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>1.205997</v>
+        <v>0.533057</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>1.971305</v>
+        <v>0.302784</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.995383</v>
+        <v>0.242909</v>
       </c>
     </row>
     <row r="49">
@@ -2459,13 +2459,13 @@
         </is>
       </c>
       <c r="B124" s="3" t="n">
-        <v>0</v>
+        <v>-0.046454</v>
       </c>
       <c r="C124" s="3" t="n">
-        <v>0</v>
+        <v>-0.046791</v>
       </c>
       <c r="D124" s="3" t="n">
-        <v>0</v>
+        <v>-0.0478</v>
       </c>
     </row>
     <row r="125">
@@ -2475,13 +2475,13 @@
         </is>
       </c>
       <c r="B125" s="3" t="n">
-        <v>0</v>
+        <v>-0.046454</v>
       </c>
       <c r="C125" s="3" t="n">
-        <v>0</v>
+        <v>-0.046791</v>
       </c>
       <c r="D125" s="3" t="n">
-        <v>0</v>
+        <v>-0.0478</v>
       </c>
     </row>
     <row r="126">
@@ -2725,7 +2725,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -4040,7 +4040,11 @@
           <t>Lease payments</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr"/>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E45" s="5" t="n">
         <v>-0.046454</v>
       </c>

--- a/output/pdf_financials_xlsx/RAIL.xlsx
+++ b/output/pdf_financials_xlsx/RAIL.xlsx
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>0.026536</v>
+        <v>-0.026536</v>
       </c>
       <c r="C17" s="3" t="n">
         <v>-0</v>
@@ -2251,13 +2251,13 @@
         </is>
       </c>
       <c r="B111" s="3" t="n">
-        <v>0</v>
+        <v>-0.013626</v>
       </c>
       <c r="C111" s="3" t="n">
-        <v>0</v>
+        <v>-0.012814</v>
       </c>
       <c r="D111" s="3" t="n">
-        <v>0</v>
+        <v>-0.007889</v>
       </c>
     </row>
     <row r="112">
@@ -2625,13 +2625,13 @@
         </is>
       </c>
       <c r="B134" s="3" t="n">
-        <v>0</v>
+        <v>-0.013626</v>
       </c>
       <c r="C134" s="3" t="n">
-        <v>0</v>
+        <v>-0.012814</v>
       </c>
       <c r="D134" s="3" t="n">
-        <v>0</v>
+        <v>-0.007889</v>
       </c>
     </row>
     <row r="135">
@@ -2641,13 +2641,13 @@
         </is>
       </c>
       <c r="B135" s="3" t="n">
-        <v>-2.428928</v>
+        <v>-2.442554</v>
       </c>
       <c r="C135" s="3" t="n">
-        <v>-5.717045</v>
+        <v>-5.729859</v>
       </c>
       <c r="D135" s="3" t="n">
-        <v>-4.300202</v>
+        <v>-4.308091</v>
       </c>
     </row>
   </sheetData>
@@ -3928,7 +3928,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr"/>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E41" s="5" t="n">
         <v>-0.013626</v>
       </c>
@@ -4855,7 +4859,11 @@
           <t>Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D72" t="inlineStr"/>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E72" s="5" t="n">
         <v>-0.026536</v>
       </c>
@@ -6279,7 +6287,11 @@
           <t>Deferred income tax recovery (Note 13)</t>
         </is>
       </c>
-      <c r="D118" t="inlineStr"/>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E118" s="5" t="n">
         <v>0.026536</v>
       </c>
